--- a/ig/mc-add-link-doc/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-add-link-doc/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:30:52+00:00</t>
+    <t>2023-05-17T07:53:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -334,7 +334,7 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Synonyme MOS : typeBAL 
+    <t>Synonyme : typeBAL 
 Valeurs possibles :
 ORG pour une BAL organisationnelle;
 APP pour une BAL applicative;
@@ -429,7 +429,7 @@
     <t>Description fonctionnelle de la boîte aux lettres.</t>
   </si>
   <si>
-    <t>Synonyme MOS : description</t>
+    <t>Synonyme : description</t>
   </si>
   <si>
     <t>Extension.extension:description.id</t>
@@ -453,7 +453,7 @@
     <t>Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
   </si>
   <si>
-    <t>Synonyme MOS : responsable</t>
+    <t>Synonyme : responsable</t>
   </si>
   <si>
     <t>Extension.extension:responsible.id</t>
@@ -477,7 +477,7 @@
     <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
   </si>
   <si>
-    <t>Synonyme MOS : serviceRattachement</t>
+    <t>Synonyme : serviceRattachement</t>
   </si>
   <si>
     <t>Extension.extension:service.id</t>
@@ -501,7 +501,7 @@
     <t>Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté.</t>
   </si>
   <si>
-    <t>Synonyme MOS : telephone</t>
+    <t>Synonyme : telephone</t>
   </si>
   <si>
     <t>Extension.extension:phone.id</t>
@@ -526,7 +526,7 @@
 - N : Dématérialisation refusée.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dematerialisation</t>
+    <t>Synonyme : dematerialisation</t>
   </si>
   <si>
     <t>Extension.extension:digitization.id</t>
@@ -555,7 +555,7 @@
 N: La boîte aux lettres peut être publiée</t>
   </si>
   <si>
-    <t>Synonyme MOS : listeRouge</t>
+    <t>Synonyme : listeRouge</t>
   </si>
   <si>
     <t>Extension.extension:publication.id</t>
